--- a/data/exports/optimization/powerball_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/powerball_genetic_optimizer_results.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-05-23 08:31:39</t>
+          <t>2026-05-24 05:36:23</t>
         </is>
       </c>
     </row>

--- a/data/exports/optimization/powerball_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/powerball_genetic_optimizer_results.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:23</t>
+          <t>2026-05-25 14:33:37</t>
         </is>
       </c>
     </row>

--- a/data/exports/optimization/powerball_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/powerball_genetic_optimizer_results.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-05-25 14:33:37</t>
+          <t>2026-05-26 14:22:56</t>
         </is>
       </c>
     </row>

--- a/data/exports/optimization/powerball_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/powerball_genetic_optimizer_results.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q54"/>
+  <dimension ref="A1:Q56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,7 +524,7 @@
         <v>45</v>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H2" t="n">
         <v>99</v>
@@ -548,7 +548,7 @@
         <v>15.0167</v>
       </c>
       <c r="O2" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
         <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H3" t="n">
         <v>99</v>
@@ -605,7 +605,7 @@
         <v>15.0167</v>
       </c>
       <c r="O3" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H4" t="n">
         <v>99</v>
@@ -662,7 +662,7 @@
         <v>15.0167</v>
       </c>
       <c r="O4" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
         <v>15.0167</v>
       </c>
       <c r="O5" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
         <v>45</v>
       </c>
       <c r="G6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H6" t="n">
         <v>99</v>
@@ -776,7 +776,7 @@
         <v>15.0167</v>
       </c>
       <c r="O6" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
         <v>45</v>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
         <v>99</v>
@@ -833,7 +833,7 @@
         <v>15.0167</v>
       </c>
       <c r="O7" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
         <v>45</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H8" t="n">
         <v>99</v>
@@ -890,7 +890,7 @@
         <v>15.0167</v>
       </c>
       <c r="O8" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
         <v>45</v>
       </c>
       <c r="G9" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>99</v>
@@ -947,7 +947,7 @@
         <v>15.0167</v>
       </c>
       <c r="O9" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
         <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H10" t="n">
         <v>99</v>
@@ -1004,7 +1004,7 @@
         <v>15.0167</v>
       </c>
       <c r="O10" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
         <v>45</v>
       </c>
       <c r="G11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
         <v>99</v>
@@ -1061,7 +1061,7 @@
         <v>15.0167</v>
       </c>
       <c r="O11" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
         <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
         <v>99</v>
@@ -1118,7 +1118,7 @@
         <v>15.0167</v>
       </c>
       <c r="O12" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         <v>45</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H13" t="n">
         <v>99</v>
@@ -1175,7 +1175,7 @@
         <v>15.0167</v>
       </c>
       <c r="O13" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
         <v>45</v>
       </c>
       <c r="G14" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
         <v>99</v>
@@ -1232,7 +1232,7 @@
         <v>15.0167</v>
       </c>
       <c r="O14" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
         <v>4</v>
@@ -1265,10 +1265,10 @@
         <v>45</v>
       </c>
       <c r="G15" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H15" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I15" t="n">
         <v>2</v>
@@ -1283,13 +1283,13 @@
         <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>15.0167</v>
+        <v>15.3052</v>
       </c>
       <c r="O15" t="n">
-        <v>257.4616</v>
+        <v>252.8631</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -1313,25 +1313,25 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="E16" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F16" t="n">
         <v>45</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="H16" t="n">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
@@ -1340,13 +1340,13 @@
         <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>15.0167</v>
+        <v>16.1864</v>
       </c>
       <c r="O16" t="n">
-        <v>257.4616</v>
+        <v>252.226</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -1364,13 +1364,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="E17" t="n">
         <v>43</v>
@@ -1379,16 +1379,16 @@
         <v>45</v>
       </c>
       <c r="G17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H17" t="n">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
         <v>3</v>
@@ -1397,13 +1397,13 @@
         <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>15.3052</v>
+        <v>13.3229</v>
       </c>
       <c r="O17" t="n">
-        <v>252.8631</v>
+        <v>252.1073</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
         <v>43</v>
@@ -1436,10 +1436,10 @@
         <v>45</v>
       </c>
       <c r="G18" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H18" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I18" t="n">
         <v>3</v>
@@ -1457,10 +1457,10 @@
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>16.1864</v>
+        <v>15.0997</v>
       </c>
       <c r="O18" t="n">
-        <v>252.106</v>
+        <v>251.1092</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -1481,13 +1481,13 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F19" t="n">
         <v>45</v>
@@ -1496,28 +1496,28 @@
         <v>17</v>
       </c>
       <c r="H19" t="n">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>15.0997</v>
+        <v>16.171</v>
       </c>
       <c r="O19" t="n">
-        <v>250.9892</v>
+        <v>250.6274</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
         <v>45</v>
       </c>
       <c r="G20" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H20" t="n">
         <v>131</v>
@@ -1574,7 +1574,7 @@
         <v>11.1131</v>
       </c>
       <c r="O20" t="n">
-        <v>248.3026</v>
+        <v>248.5426</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
         <v>43</v>
       </c>
       <c r="G21" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H21" t="n">
         <v>90</v>
@@ -1631,7 +1631,7 @@
         <v>11.4127</v>
       </c>
       <c r="O21" t="n">
-        <v>247.4918</v>
+        <v>247.7318</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
         <v>11.4127</v>
       </c>
       <c r="O22" t="n">
-        <v>247.4918</v>
+        <v>247.7318</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
         <v>11.2916</v>
       </c>
       <c r="O23" t="n">
-        <v>246.669</v>
+        <v>246.909</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
         <v>45</v>
       </c>
       <c r="G24" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H24" t="n">
         <v>104</v>
@@ -1802,7 +1802,7 @@
         <v>12.2678</v>
       </c>
       <c r="O24" t="n">
-        <v>246.0296</v>
+        <v>246.1496</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
         <v>45</v>
       </c>
       <c r="G25" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H25" t="n">
         <v>104</v>
@@ -1859,7 +1859,7 @@
         <v>12.2678</v>
       </c>
       <c r="O25" t="n">
-        <v>246.0296</v>
+        <v>246.1496</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -1880,10 +1880,10 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E26" t="n">
         <v>43</v>
@@ -1892,10 +1892,10 @@
         <v>45</v>
       </c>
       <c r="G26" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H26" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I26" t="n">
         <v>2</v>
@@ -1904,19 +1904,19 @@
         <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>13.9104</v>
+        <v>12.2678</v>
       </c>
       <c r="O26" t="n">
-        <v>245.2961</v>
+        <v>246.1496</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
         <v>16.171</v>
       </c>
       <c r="O27" t="n">
-        <v>244.4274</v>
+        <v>244.5474</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
         <v>45</v>
       </c>
       <c r="G28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H28" t="n">
         <v>97</v>
@@ -2030,7 +2030,7 @@
         <v>15.0499</v>
       </c>
       <c r="O28" t="n">
-        <v>243.3448</v>
+        <v>243.4648</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
         <v>45</v>
       </c>
       <c r="G29" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H29" t="n">
         <v>108</v>
@@ -2087,7 +2087,7 @@
         <v>10.4163</v>
       </c>
       <c r="O29" t="n">
-        <v>242.6008</v>
+        <v>242.7208</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -2105,25 +2105,25 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F30" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G30" t="n">
         <v>17</v>
       </c>
       <c r="H30" t="n">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="I30" t="n">
         <v>2</v>
@@ -2132,19 +2132,19 @@
         <v>3</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>9.443899999999999</v>
+        <v>15.6045</v>
       </c>
       <c r="O30" t="n">
-        <v>242.3698</v>
+        <v>242.4112</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -2162,25 +2162,25 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E31" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F31" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G31" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H31" t="n">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="I31" t="n">
         <v>2</v>
@@ -2189,19 +2189,19 @@
         <v>3</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>15.6045</v>
+        <v>9.443899999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>242.2912</v>
+        <v>242.3698</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
         <v>45</v>
       </c>
       <c r="G32" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H32" t="n">
         <v>128</v>
@@ -2258,7 +2258,7 @@
         <v>9.120699999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>242.1218</v>
+        <v>242.2418</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
         <v>45</v>
       </c>
       <c r="G33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H33" t="n">
         <v>113</v>
@@ -2315,7 +2315,7 @@
         <v>8.859999999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>242.0701</v>
+        <v>242.1901</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -2336,28 +2336,28 @@
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E34" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="F34" t="n">
         <v>45</v>
       </c>
       <c r="G34" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H34" t="n">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
         <v>3</v>
@@ -2369,10 +2369,10 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>14.4395</v>
+        <v>7.7782</v>
       </c>
       <c r="O34" t="n">
-        <v>239.6588</v>
+        <v>241.0054</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -2399,16 +2399,16 @@
         <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F35" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G35" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
@@ -2423,13 +2423,13 @@
         <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>14.7394</v>
+        <v>14.4395</v>
       </c>
       <c r="O35" t="n">
-        <v>239.2885</v>
+        <v>239.9388</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -2453,40 +2453,40 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="F36" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G36" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H36" t="n">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>9.354100000000001</v>
+        <v>14.7394</v>
       </c>
       <c r="O36" t="n">
-        <v>238.9054</v>
+        <v>239.4085</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -2507,28 +2507,28 @@
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F37" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H37" t="n">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K37" t="n">
         <v>3</v>
@@ -2540,10 +2540,10 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>7.6485</v>
+        <v>13.0096</v>
       </c>
       <c r="O37" t="n">
-        <v>238.8813</v>
+        <v>239.324</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -2561,13 +2561,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E38" t="n">
         <v>43</v>
@@ -2576,31 +2576,31 @@
         <v>45</v>
       </c>
       <c r="G38" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H38" t="n">
         <v>122</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>8.2576</v>
+        <v>9.354100000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>238.6839</v>
+        <v>239.1454</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -2618,46 +2618,46 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E39" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="F39" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G39" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H39" t="n">
-        <v>57</v>
+        <v>122</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>15.3052</v>
+        <v>8.2576</v>
       </c>
       <c r="O39" t="n">
-        <v>238.4231</v>
+        <v>238.6839</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
         <v>45</v>
       </c>
       <c r="G40" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H40" t="n">
         <v>66</v>
@@ -2714,7 +2714,7 @@
         <v>13.8744</v>
       </c>
       <c r="O40" t="n">
-        <v>237.7661</v>
+        <v>237.8861</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -2735,43 +2735,43 @@
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="F41" t="n">
         <v>45</v>
       </c>
       <c r="G41" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H41" t="n">
-        <v>124</v>
+        <v>66</v>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>8.2158</v>
+        <v>13.8744</v>
       </c>
       <c r="O41" t="n">
-        <v>237.0596</v>
+        <v>237.8861</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
         <v>45</v>
       </c>
       <c r="G42" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
         <v>89</v>
@@ -2828,7 +2828,7 @@
         <v>10.025</v>
       </c>
       <c r="O42" t="n">
-        <v>236.7424</v>
+        <v>236.8624</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
         <v>10.025</v>
       </c>
       <c r="O43" t="n">
-        <v>236.7424</v>
+        <v>236.8624</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
         <v>43</v>
       </c>
       <c r="G44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H44" t="n">
         <v>64</v>
@@ -2942,7 +2942,7 @@
         <v>13.0096</v>
       </c>
       <c r="O44" t="n">
-        <v>235.564</v>
+        <v>235.684</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
         <v>45</v>
       </c>
       <c r="G45" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
         <v>114</v>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
         <v>12.7475</v>
       </c>
       <c r="O46" t="n">
-        <v>234.7889</v>
+        <v>234.9089</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
         <v>45</v>
       </c>
       <c r="G47" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H47" t="n">
         <v>76</v>
@@ -3113,7 +3113,7 @@
         <v>9.354100000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>234.6654</v>
+        <v>234.7854</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>45</v>
       </c>
       <c r="G48" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H48" t="n">
         <v>122</v>
@@ -3170,7 +3170,7 @@
         <v>7.7782</v>
       </c>
       <c r="O48" t="n">
-        <v>233.8854</v>
+        <v>234.1254</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -3191,10 +3191,10 @@
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E49" t="n">
         <v>43</v>
@@ -3203,10 +3203,10 @@
         <v>45</v>
       </c>
       <c r="G49" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H49" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="I49" t="n">
         <v>2</v>
@@ -3215,19 +3215,19 @@
         <v>3</v>
       </c>
       <c r="K49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>9.354100000000001</v>
+        <v>7.5829</v>
       </c>
       <c r="O49" t="n">
-        <v>232.5454</v>
+        <v>234.1172</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
         <v>4</v>
       </c>
       <c r="D50" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E50" t="n">
         <v>43</v>
@@ -3260,16 +3260,16 @@
         <v>45</v>
       </c>
       <c r="G50" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H50" t="n">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K50" t="n">
         <v>3</v>
@@ -3281,10 +3281,10 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>8.6891</v>
+        <v>9.354100000000001</v>
       </c>
       <c r="O50" t="n">
-        <v>230.2027</v>
+        <v>232.6654</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -3302,25 +3302,25 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E51" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F51" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H51" t="n">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="I51" t="n">
         <v>3</v>
@@ -3329,19 +3329,19 @@
         <v>2</v>
       </c>
       <c r="K51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>15.0167</v>
+        <v>8.6891</v>
       </c>
       <c r="O51" t="n">
-        <v>229.9416</v>
+        <v>230.3227</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -3359,25 +3359,25 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D52" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E52" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F52" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G52" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H52" t="n">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="I52" t="n">
         <v>2</v>
@@ -3395,10 +3395,10 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>9.2331</v>
+        <v>8.3179</v>
       </c>
       <c r="O52" t="n">
-        <v>228.8827</v>
+        <v>230.0348</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -3416,46 +3416,46 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="E53" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F53" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G53" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H53" t="n">
-        <v>75</v>
+        <v>146</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>9.669499999999999</v>
+        <v>15.0167</v>
       </c>
       <c r="O53" t="n">
-        <v>223.2938</v>
+        <v>229.9416</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-05-26 14:22:56</t>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -3482,46 +3482,160 @@
         <v>6</v>
       </c>
       <c r="E54" t="n">
+        <v>31</v>
+      </c>
+      <c r="F54" t="n">
+        <v>43</v>
+      </c>
+      <c r="G54" t="n">
+        <v>17</v>
+      </c>
+      <c r="H54" t="n">
+        <v>85</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2</v>
+      </c>
+      <c r="J54" t="n">
+        <v>3</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>9.2331</v>
+      </c>
+      <c r="O54" t="n">
+        <v>229.1627</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>GeneticPOWERBALLOptimizer_v1</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>4</v>
+      </c>
+      <c r="D55" t="n">
+        <v>6</v>
+      </c>
+      <c r="E55" t="n">
+        <v>19</v>
+      </c>
+      <c r="F55" t="n">
+        <v>45</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2</v>
+      </c>
+      <c r="H55" t="n">
+        <v>75</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>4</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3</v>
+      </c>
+      <c r="L55" t="n">
+        <v>2</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>9.669499999999999</v>
+      </c>
+      <c r="O55" t="n">
+        <v>223.4138</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>GeneticPOWERBALLOptimizer_v1</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>4</v>
+      </c>
+      <c r="D56" t="n">
+        <v>6</v>
+      </c>
+      <c r="E56" t="n">
         <v>16</v>
       </c>
-      <c r="F54" t="n">
-        <v>45</v>
-      </c>
-      <c r="G54" t="n">
-        <v>8</v>
-      </c>
-      <c r="H54" t="n">
+      <c r="F56" t="n">
+        <v>45</v>
+      </c>
+      <c r="G56" t="n">
+        <v>15</v>
+      </c>
+      <c r="H56" t="n">
         <v>72</v>
       </c>
-      <c r="I54" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" t="n">
-        <v>4</v>
-      </c>
-      <c r="K54" t="n">
-        <v>2</v>
-      </c>
-      <c r="L54" t="n">
-        <v>3</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>4</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2</v>
+      </c>
+      <c r="L56" t="n">
+        <v>3</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
         <v>10.8397</v>
       </c>
-      <c r="O54" t="n">
-        <v>217.1794</v>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>GeneticPOWERBALLOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>2026-05-26 14:22:56</t>
+      <c r="O56" t="n">
+        <v>217.2994</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>GeneticPOWERBALLOptimizer_v1</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>2026-05-27 14:57:48</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3678,7 @@
         <v>242.5586</v>
       </c>
       <c r="C2" t="n">
-        <v>213.6858</v>
+        <v>213.8234</v>
       </c>
     </row>
     <row r="3">
@@ -3572,10 +3686,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>250.0195</v>
+        <v>247.604</v>
       </c>
       <c r="C3" t="n">
-        <v>225.462</v>
+        <v>226.8873</v>
       </c>
     </row>
     <row r="4">
@@ -3583,10 +3697,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>251.3273</v>
+        <v>251.7774</v>
       </c>
       <c r="C4" t="n">
-        <v>232.9221</v>
+        <v>234.6498</v>
       </c>
     </row>
     <row r="5">
@@ -3594,10 +3708,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>253.6461</v>
+        <v>255.2174</v>
       </c>
       <c r="C5" t="n">
-        <v>238.3583</v>
+        <v>239.4636</v>
       </c>
     </row>
     <row r="6">
@@ -3605,10 +3719,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>254.4461</v>
+        <v>257.5816</v>
       </c>
       <c r="C6" t="n">
-        <v>242.2397</v>
+        <v>242.654</v>
       </c>
     </row>
     <row r="7">
@@ -3616,10 +3730,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C7" t="n">
-        <v>244.976</v>
+        <v>243.1508</v>
       </c>
     </row>
     <row r="8">
@@ -3627,10 +3741,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C8" t="n">
-        <v>243.9859</v>
+        <v>244.7333</v>
       </c>
     </row>
     <row r="9">
@@ -3638,10 +3752,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C9" t="n">
-        <v>246.424</v>
+        <v>249.7494</v>
       </c>
     </row>
     <row r="10">
@@ -3649,10 +3763,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C10" t="n">
-        <v>250.3585</v>
+        <v>251.8605</v>
       </c>
     </row>
     <row r="11">
@@ -3660,10 +3774,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C11" t="n">
-        <v>248.7993</v>
+        <v>254.2464</v>
       </c>
     </row>
     <row r="12">
@@ -3671,10 +3785,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C12" t="n">
-        <v>249.7224</v>
+        <v>254.9988</v>
       </c>
     </row>
     <row r="13">
@@ -3682,10 +3796,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C13" t="n">
-        <v>252.2924</v>
+        <v>254.6847</v>
       </c>
     </row>
     <row r="14">
@@ -3693,10 +3807,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C14" t="n">
-        <v>250.7492</v>
+        <v>254.6438</v>
       </c>
     </row>
     <row r="15">
@@ -3704,10 +3818,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C15" t="n">
-        <v>249.8429</v>
+        <v>255.7954</v>
       </c>
     </row>
     <row r="16">
@@ -3715,10 +3829,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C16" t="n">
-        <v>254.8817</v>
+        <v>254.9656</v>
       </c>
     </row>
     <row r="17">
@@ -3726,10 +3840,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C17" t="n">
-        <v>255.0313</v>
+        <v>255.0621</v>
       </c>
     </row>
     <row r="18">
@@ -3737,10 +3851,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C18" t="n">
-        <v>254.0388</v>
+        <v>254.3897</v>
       </c>
     </row>
     <row r="19">
@@ -3748,10 +3862,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C19" t="n">
-        <v>254.5265</v>
+        <v>254.444</v>
       </c>
     </row>
     <row r="20">
@@ -3759,10 +3873,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C20" t="n">
-        <v>254.6065</v>
+        <v>254.9063</v>
       </c>
     </row>
     <row r="21">
@@ -3770,10 +3884,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C21" t="n">
-        <v>254.7746</v>
+        <v>254.8418</v>
       </c>
     </row>
     <row r="22">
@@ -3781,10 +3895,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C22" t="n">
-        <v>254.7938</v>
+        <v>254.7115</v>
       </c>
     </row>
     <row r="23">
@@ -3792,10 +3906,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C23" t="n">
-        <v>254.7988</v>
+        <v>255.2056</v>
       </c>
     </row>
     <row r="24">
@@ -3803,10 +3917,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C24" t="n">
-        <v>254.5449</v>
+        <v>254.7324</v>
       </c>
     </row>
     <row r="25">
@@ -3814,10 +3928,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C25" t="n">
-        <v>254.9934</v>
+        <v>255.0046</v>
       </c>
     </row>
     <row r="26">
@@ -3825,10 +3939,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C26" t="n">
-        <v>254.1856</v>
+        <v>254.3274</v>
       </c>
     </row>
     <row r="27">
@@ -3836,10 +3950,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C27" t="n">
-        <v>253.6761</v>
+        <v>253.9206</v>
       </c>
     </row>
     <row r="28">
@@ -3847,10 +3961,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C28" t="n">
-        <v>255.4088</v>
+        <v>255.1684</v>
       </c>
     </row>
     <row r="29">
@@ -3858,10 +3972,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C29" t="n">
-        <v>254.506</v>
+        <v>254.513</v>
       </c>
     </row>
     <row r="30">
@@ -3869,10 +3983,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C30" t="n">
-        <v>253.5829</v>
+        <v>254.4178</v>
       </c>
     </row>
     <row r="31">
@@ -3880,10 +3994,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C31" t="n">
-        <v>254.5583</v>
+        <v>254.5872</v>
       </c>
     </row>
     <row r="32">
@@ -3891,10 +4005,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C32" t="n">
-        <v>254.9626</v>
+        <v>254.4312</v>
       </c>
     </row>
     <row r="33">
@@ -3902,10 +4016,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C33" t="n">
-        <v>255.4541</v>
+        <v>255.6626</v>
       </c>
     </row>
     <row r="34">
@@ -3913,10 +4027,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C34" t="n">
-        <v>254.1738</v>
+        <v>254.572</v>
       </c>
     </row>
     <row r="35">
@@ -3924,10 +4038,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C35" t="n">
-        <v>254.9927</v>
+        <v>254.9896</v>
       </c>
     </row>
     <row r="36">
@@ -3935,10 +4049,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C36" t="n">
-        <v>254.2134</v>
+        <v>254.738</v>
       </c>
     </row>
     <row r="37">
@@ -3946,10 +4060,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C37" t="n">
-        <v>255.0308</v>
+        <v>254.8974</v>
       </c>
     </row>
     <row r="38">
@@ -3957,10 +4071,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C38" t="n">
-        <v>255.2935</v>
+        <v>255.1885</v>
       </c>
     </row>
     <row r="39">
@@ -3968,10 +4082,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C39" t="n">
-        <v>254.5766</v>
+        <v>254.838</v>
       </c>
     </row>
     <row r="40">
@@ -3979,10 +4093,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C40" t="n">
-        <v>254.9939</v>
+        <v>255.2089</v>
       </c>
     </row>
     <row r="41">
@@ -3990,10 +4104,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C41" t="n">
-        <v>254.0161</v>
+        <v>254.278</v>
       </c>
     </row>
     <row r="42">
@@ -4001,10 +4115,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C42" t="n">
-        <v>254.3966</v>
+        <v>254.4875</v>
       </c>
     </row>
     <row r="43">
@@ -4012,10 +4126,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C43" t="n">
-        <v>254.8891</v>
+        <v>254.759</v>
       </c>
     </row>
     <row r="44">
@@ -4023,10 +4137,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C44" t="n">
-        <v>254.6708</v>
+        <v>254.6769</v>
       </c>
     </row>
     <row r="45">
@@ -4034,10 +4148,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C45" t="n">
-        <v>254.0808</v>
+        <v>254.5552</v>
       </c>
     </row>
     <row r="46">
@@ -4045,10 +4159,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C46" t="n">
-        <v>254.8188</v>
+        <v>254.9098</v>
       </c>
     </row>
     <row r="47">
@@ -4056,10 +4170,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C47" t="n">
-        <v>254.7132</v>
+        <v>254.4665</v>
       </c>
     </row>
     <row r="48">
@@ -4067,10 +4181,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C48" t="n">
-        <v>254.4463</v>
+        <v>254.9738</v>
       </c>
     </row>
     <row r="49">
@@ -4078,10 +4192,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C49" t="n">
-        <v>254.948</v>
+        <v>254.6695</v>
       </c>
     </row>
     <row r="50">
@@ -4089,10 +4203,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C50" t="n">
-        <v>253.8633</v>
+        <v>254.3363</v>
       </c>
     </row>
     <row r="51">
@@ -4100,10 +4214,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C51" t="n">
-        <v>254.3744</v>
+        <v>254.2978</v>
       </c>
     </row>
     <row r="52">
@@ -4111,10 +4225,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C52" t="n">
-        <v>255.5135</v>
+        <v>255.6666</v>
       </c>
     </row>
     <row r="53">
@@ -4122,10 +4236,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C53" t="n">
-        <v>253.791</v>
+        <v>253.8536</v>
       </c>
     </row>
     <row r="54">
@@ -4133,10 +4247,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C54" t="n">
-        <v>254.487</v>
+        <v>254.6737</v>
       </c>
     </row>
     <row r="55">
@@ -4144,10 +4258,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C55" t="n">
-        <v>253.9763</v>
+        <v>254.0453</v>
       </c>
     </row>
     <row r="56">
@@ -4155,10 +4269,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C56" t="n">
-        <v>254.6316</v>
+        <v>254.7406</v>
       </c>
     </row>
     <row r="57">
@@ -4166,10 +4280,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C57" t="n">
-        <v>254.2992</v>
+        <v>254.4868</v>
       </c>
     </row>
     <row r="58">
@@ -4177,10 +4291,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C58" t="n">
-        <v>254.1395</v>
+        <v>254.1502</v>
       </c>
     </row>
     <row r="59">
@@ -4188,10 +4302,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C59" t="n">
-        <v>254.6379</v>
+        <v>254.5062</v>
       </c>
     </row>
     <row r="60">
@@ -4199,10 +4313,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C60" t="n">
-        <v>254.6255</v>
+        <v>255.0407</v>
       </c>
     </row>
     <row r="61">
@@ -4210,10 +4324,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>257.4616</v>
+        <v>257.5816</v>
       </c>
       <c r="C61" t="n">
-        <v>254.3837</v>
+        <v>254.7383</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/optimization/powerball_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/powerball_genetic_optimizer_results.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026-05-27 14:57:48</t>
+          <t>2026-05-28 08:53:44</t>
         </is>
       </c>
     </row>

--- a/data/exports/optimization/powerball_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/powerball_genetic_optimizer_results.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026-05-28 08:53:44</t>
+          <t>2026-05-28 17:21:50</t>
         </is>
       </c>
     </row>

--- a/data/exports/optimization/powerball_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/powerball_genetic_optimizer_results.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026-05-28 17:21:50</t>
+          <t>2026-05-28 19:49:12</t>
         </is>
       </c>
     </row>
